--- a/data/trans_orig/IP25-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79824</t>
+          <t>79091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87613</t>
+          <t>87214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71571</t>
+          <t>71621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155120</t>
+          <t>155177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167339</t>
+          <t>167228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368828</t>
+          <t>369865</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387835</t>
+          <t>387151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>412356</t>
+          <t>412405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>434283</t>
+          <t>434027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>785718</t>
+          <t>786754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>817449</t>
+          <t>815354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>28936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>46222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42708</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64635</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75629</t>
+          <t>77724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107360</t>
+          <t>106324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142143</t>
+          <t>142649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156735</t>
+          <t>157057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122501</t>
+          <t>122624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137643</t>
+          <t>137663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>270513</t>
+          <t>271008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291745</t>
+          <t>290850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>29973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>35514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39016</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60248</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>601092</t>
+          <t>600298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>625225</t>
+          <t>625132</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>616844</t>
+          <t>615605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>645449</t>
+          <t>644367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1225306</t>
+          <t>1226147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1265460</t>
+          <t>1264345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54352</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>79279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76525</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105130</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136091</t>
+          <t>137206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176245</t>
+          <t>175404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81508</t>
+          <t>81973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89626</t>
+          <t>89574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76722</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84209</t>
+          <t>84298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>161781</t>
+          <t>161842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172461</t>
+          <t>172763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>385368</t>
+          <t>385105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>407448</t>
+          <t>407992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439533</t>
+          <t>439568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>460236</t>
+          <t>460482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>831736</t>
+          <t>832913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>863774</t>
+          <t>862866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>43277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>51852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78915</t>
+          <t>79823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110953</t>
+          <t>109776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142128</t>
+          <t>141519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154910</t>
+          <t>155085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143606</t>
+          <t>143598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157969</t>
+          <t>157541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>291330</t>
+          <t>289485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309109</t>
+          <t>308888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24684</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29932</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>49556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>617612</t>
+          <t>618615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>645912</t>
+          <t>646696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>671495</t>
+          <t>671132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>696835</t>
+          <t>696662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1298305</t>
+          <t>1298752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1336439</t>
+          <t>1335385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>91835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>53179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78346</t>
+          <t>78709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123851</t>
+          <t>124905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161985</t>
+          <t>161538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>48502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>56145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61091</t>
+          <t>60919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>67292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112309</t>
+          <t>112201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122126</t>
+          <t>122468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>420414</t>
+          <t>420160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439453</t>
+          <t>439575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>441448</t>
+          <t>442762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>460546</t>
+          <t>461170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>869461</t>
+          <t>869465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>896185</t>
+          <t>896864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>32715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51876</t>
+          <t>52130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>45973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91564</t>
+          <t>91560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>140434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155304</t>
+          <t>155534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153583</t>
+          <t>154525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169098</t>
+          <t>169552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>300971</t>
+          <t>300679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321128</t>
+          <t>321862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32078</t>
+          <t>32269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>618103</t>
+          <t>618652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>644853</t>
+          <t>644628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>666379</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>691435</t>
+          <t>691607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1292026</t>
+          <t>1294340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1329840</t>
+          <t>1330065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78465</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119375</t>
+          <t>119150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157189</t>
+          <t>154875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
